--- a/Result/profitability/3623.xlsx
+++ b/Result/profitability/3623.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1075</v>
+        <v>0.20875</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1475</v>
+        <v>1.79375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22375</v>
+        <v>0.30375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.99125</v>
+        <v>4.52625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3175</v>
+        <v>0.4</v>
       </c>
       <c r="N4" t="n">
-        <v>8.52375</v>
+        <v>7.125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.36625</v>
+        <v>0.43625</v>
       </c>
       <c r="N5" t="n">
-        <v>10.275</v>
+        <v>8.477500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.09999999999999</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3774999999999999</v>
+        <v>0.39625</v>
       </c>
       <c r="N6" t="n">
-        <v>10.76625</v>
+        <v>10.4175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3875</v>
+        <v>0.42625</v>
       </c>
       <c r="N7" t="n">
-        <v>14.10625</v>
+        <v>13.45875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4425</v>
+        <v>0.4575</v>
       </c>
       <c r="N8" t="n">
-        <v>16.7625</v>
+        <v>14.24125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3623</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>51</v>
+      </c>
+      <c r="D74" t="n">
+        <v>56</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-24.30%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>23</v>
+      </c>
+      <c r="J74" t="n">
+        <v>11</v>
+      </c>
+      <c r="K74" t="n">
+        <v>11</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.02625000000000001</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-3.4475</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-20.17</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-1.979391560353288</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-3.111111111111111</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-14.38</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-3.268181818181818</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
